--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bstevens/Downloads/Hilltop-Manor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F6ADE30-5904-B244-A707-5192A711B650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57F13BB9-C709-D847-95B8-9724227CCD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="151">
   <si>
     <t>Hilltop Manor: guest codes</t>
   </si>
@@ -68,6 +68,15 @@
     <t>Dress</t>
   </si>
   <si>
+    <t>Act1</t>
+  </si>
+  <si>
+    <t>Act2</t>
+  </si>
+  <si>
+    <t>Act3</t>
+  </si>
+  <si>
     <t>Murderer</t>
   </si>
   <si>
@@ -471,6 +480,15 @@
   </si>
   <si>
     <t>Have fun with some 1920s attire!  You can dress however you want to the event.</t>
+  </si>
+  <si>
+    <t>We welcome you to the funeral.</t>
+  </si>
+  <si>
+    <t>A surprising conclussion to our evening!</t>
+  </si>
+  <si>
+    <t>A mystery unfolds!</t>
   </si>
 </sst>
 </file>
@@ -1022,20 +1040,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="48" customWidth="1"/>
     <col min="4" max="5" width="96" customWidth="1"/>
-    <col min="6" max="6" width="46" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="58" customWidth="1"/>
-    <col min="9" max="9" width="54" customWidth="1"/>
+    <col min="6" max="9" width="46" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="58" customWidth="1"/>
+    <col min="12" max="12" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1">
+    <row r="1" spans="1:12" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
@@ -1063,472 +1081,634 @@
       <c r="I1" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="104" customHeight="1">
+      <c r="J1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="104" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H2" s="8"/>
+        <v>147</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="I2" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="104" customHeight="1">
+        <v>149</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="104" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="104" customHeight="1">
+        <v>147</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="104" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H4" s="8"/>
+        <v>147</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="I4" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="104" customHeight="1">
+        <v>149</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="104" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="104" customHeight="1">
+        <v>147</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="104" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="H6" s="8"/>
+        <v>147</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="I6" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="104" customHeight="1">
+        <v>149</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="104" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="104" customHeight="1">
+        <v>147</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="104" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H8" s="8"/>
+        <v>147</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="I8" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="104" customHeight="1">
+        <v>149</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="104" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="104" customHeight="1">
+        <v>147</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="104" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H10" s="8"/>
+        <v>147</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="I10" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="104" customHeight="1">
+        <v>149</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="104" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="104" customHeight="1">
+        <v>147</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="104" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H12" s="8"/>
+        <v>147</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="I12" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="104" customHeight="1">
+        <v>149</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="104" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="104" customHeight="1">
+        <v>147</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="104" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H14" s="8"/>
+        <v>147</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="I14" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="112" customHeight="1">
+        <v>149</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="112" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="112" customHeight="1">
+        <v>147</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="112" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H16" s="8"/>
+        <v>147</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="I16" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="126" customHeight="1">
+        <v>149</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="126" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="112" customHeight="1">
+        <v>147</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="112" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H18" s="8"/>
+        <v>147</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="I18" s="8" t="s">
-        <v>114</v>
+        <v>149</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G18">
+  <conditionalFormatting sqref="J2:J18">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="YES"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="G2:G100" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="J2:J100" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"UNASSIGNED,YES,NO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1547,26 +1727,26 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="34" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="34" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1585,87 +1765,87 @@
   <sheetData>
     <row r="2" spans="1:2" ht="20">
       <c r="A2" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="72" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="72" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="72" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="72" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="72" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="72" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="72" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="72" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="72" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="72" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bstevens/Downloads/Hilltop-Manor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57F13BB9-C709-D847-95B8-9724227CCD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABC8D23E-7271-4F44-BC03-CE41B0C713E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest Codes" sheetId="1" r:id="rId1"/>
@@ -221,9 +221,6 @@
     <t>[red]Funeral director’s assistant[/red]</t>
   </si>
   <si>
-    <t>[red]“Me? I’m just a humble assistant to Mr Graves. He took me in off the street, he did. I never had any family or friends. He might be a queer sort of fellow, but he’s very kind to me. I’d never say a bad word about him or the mysterious things that go on at the mortuary.”[/red]</t>
-  </si>
-  <si>
     <t>You’re a salt of the earth former street urchin. Proclaim your amazement at everything from spoons to furniture. Ask what they are and marvel at how the other half live. Ask people the meaning of words all the time too.</t>
   </si>
   <si>
@@ -365,9 +362,6 @@
     <t>[red]Worker in a general store run by your parents[/red]</t>
   </si>
   <si>
-    <t>[red]Your true passion is in your operations as a healer and psychic. You like to distribute flyers advertising your supernatural powers and ability to cure diseases. You also conduct séances and give lectures on spiritualism, including advocating for free love. You love spending time in your garden, where you grow a variety of plants and flowers used in herbal remedies for a variety of maladies.[/red]</t>
-  </si>
-  <si>
     <t>You consider yourself responsible to no man and to no law but yourself. You think there are times when even murder might be good, brave, noble, and humane. You also denounce other social “norms” such as saying “bless you” after someone sneezes, giving up your seat for the elderly and pregnant, regular bathing, and shaming familial relations. You are always on the hunt for substances that you can compost into fertilizer for your garden; really any (previously) living thing will provide a good source of nitrogen and other nutrients for your plants.</t>
   </si>
   <si>
@@ -383,12 +377,6 @@
     <t>[red]Owner of a pig farm[/red]</t>
   </si>
   <si>
-    <t>[red]After the passing of your late husband, Peter, who tragically passed after a meat grinder fell on his head when he was reaching for an item on the top shelf, you used his life insurance money to buy some land and start a farm.[/red]</t>
-  </si>
-  <si>
-    <t>[red]You pride yourself on your physical strength. You work out every day on the farm by moving farm equipment and by lifting carcasses – animal carcasses, of course. While Peter will always be in your heart, you are ready to seek love again, and you regularly place marriage ads in the newspapers. While you have had several eager men respond to your advertisements, you’ve yet to find a man worth marrying.[/red]</t>
-  </si>
-  <si>
     <t>Screenshot 2026-09-26 at 3.33.33 PM.png</t>
   </si>
   <si>
@@ -489,6 +477,18 @@
   </si>
   <si>
     <t>A mystery unfolds!</t>
+  </si>
+  <si>
+    <t>[red]“Me? I’m just a humble assistant to Mr Graves. He took me in off the street, he did. I never had any family or friends. He might be a unique sort of fellow, but he’s very kind to me. I’d never say a bad word about him or the mysterious things that go on at the mortuary.”[/red]</t>
+  </si>
+  <si>
+    <t>[red] You pride yourself on your physical strength. You work out every day on the farm by moving farm equipment and by lifting carcasses – animal carcasses, of course. While Peter will always be in your heart, you are ready to seek love again, and you regularly place marriage ads in the newspapers. While you have had several eager men respond to your advertisements, you’ve yet to find a man worth marrying. [/red]</t>
+  </si>
+  <si>
+    <t>[red]After the passing of your late husband, Peter, who tragically passed after a meat grinder fell on his head when he was reaching for an item on the top shelf, you used his life insurance money to buy some land and start a farm. [/red]</t>
+  </si>
+  <si>
+    <t>[red]Your true passion is in your operations as a healer and psychic. You like to distribute flyers advertising your supernatural powers and ability to cure diseases. You also conduct seances and give lectures on spiritualism, including advocating for free love. You love spending time in your garden, where you grow a variety of plants and flowers used in herbal remedies for a variety of maladies.[/red]</t>
   </si>
 </sst>
 </file>
@@ -1108,19 +1108,19 @@
         <v>20</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8" t="s">
@@ -1144,19 +1144,19 @@
         <v>26</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
@@ -1180,19 +1180,19 @@
         <v>32</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8" t="s">
@@ -1216,19 +1216,19 @@
         <v>38</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4" t="s">
@@ -1252,19 +1252,19 @@
         <v>44</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8" t="s">
@@ -1288,19 +1288,19 @@
         <v>50</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="s">
@@ -1324,19 +1324,19 @@
         <v>56</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8" t="s">
@@ -1354,353 +1354,353 @@
         <v>60</v>
       </c>
       <c r="D9" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="F9" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="104" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="F10" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="104" customHeight="1">
       <c r="A11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="C11" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="D11" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="E11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="F11" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="104" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="C12" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>80</v>
-      </c>
       <c r="F12" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="104" customHeight="1">
       <c r="A13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="C13" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="D13" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="F13" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="104" customHeight="1">
       <c r="A14" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="C14" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>92</v>
-      </c>
       <c r="F14" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="112" customHeight="1">
       <c r="A15" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="C15" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="D15" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="E15" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>98</v>
-      </c>
       <c r="F15" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="112" customHeight="1">
       <c r="A16" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="D16" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="F16" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="126" customHeight="1">
       <c r="A17" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="C17" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="D17" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>110</v>
-      </c>
       <c r="F17" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="112" customHeight="1">
       <c r="A18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>114</v>
-      </c>
       <c r="D18" s="9" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1727,26 +1727,26 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="34" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="34" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1765,87 +1765,87 @@
   <sheetData>
     <row r="2" spans="1:2" ht="20">
       <c r="A2" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="72" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="72" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="72" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="72" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="72" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="72" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="72" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="72" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="72" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="72" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bstevens/Downloads/Hilltop-Manor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABC8D23E-7271-4F44-BC03-CE41B0C713E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1818BC89-D4A1-6A44-AD44-5DB6BAE53C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -479,9 +479,6 @@
     <t>A mystery unfolds!</t>
   </si>
   <si>
-    <t>[red]“Me? I’m just a humble assistant to Mr Graves. He took me in off the street, he did. I never had any family or friends. He might be a unique sort of fellow, but he’s very kind to me. I’d never say a bad word about him or the mysterious things that go on at the mortuary.”[/red]</t>
-  </si>
-  <si>
     <t>[red] You pride yourself on your physical strength. You work out every day on the farm by moving farm equipment and by lifting carcasses – animal carcasses, of course. While Peter will always be in your heart, you are ready to seek love again, and you regularly place marriage ads in the newspapers. While you have had several eager men respond to your advertisements, you’ve yet to find a man worth marrying. [/red]</t>
   </si>
   <si>
@@ -489,6 +486,9 @@
   </si>
   <si>
     <t>[red]Your true passion is in your operations as a healer and psychic. You like to distribute flyers advertising your supernatural powers and ability to cure diseases. You also conduct seances and give lectures on spiritualism, including advocating for free love. You love spending time in your garden, where you grow a variety of plants and flowers used in herbal remedies for a variety of maladies.[/red]</t>
+  </si>
+  <si>
+    <t>[red]“Me? I’m just a humble assistant to Mr. Graves. He took me in off the street, he did. I never had any family or friends. He might be a unique sort of fellow, but he’s very kind to me. I’d never say a bad word about him or the mysterious things that go on at the mortuary.”[/red]</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1354,7 @@
         <v>60</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>61</v>
@@ -1642,7 +1642,7 @@
         <v>107</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>108</v>
@@ -1678,10 +1678,10 @@
         <v>112</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>143</v>
